--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484546_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484546_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1124</v>
+        <v>9.070499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8106</v>
+        <v>5.1899</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3018</v>
+        <v>3.8806</v>
       </c>
       <c r="G2" t="n">
         <v>5.0894</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0805</v>
+        <v>2.0386</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9653</v>
+        <v>1.3447</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1151</v>
+        <v>0.694</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6231</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6256</v>
+        <v>6.7272</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5582</v>
+        <v>4.7095</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0673</v>
+        <v>2.0178</v>
       </c>
       <c r="G3" t="n">
         <v>1.8471</v>
@@ -688,13 +688,13 @@
         <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3961</v>
+        <v>1.4977</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3907</v>
+        <v>1.5419</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0054</v>
+        <v>-0.0441</v>
       </c>
       <c r="V3" t="n">
         <v>0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3842</v>
+        <v>6.2322</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8281</v>
+        <v>3.1716</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5561</v>
+        <v>3.0607</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9618</v>
@@ -766,13 +766,13 @@
         <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4193</v>
+        <v>2.2673</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3537</v>
+        <v>1.6972</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0656</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>2.5444</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8594</v>
+        <v>5.2062</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1489</v>
+        <v>4.2974</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7105</v>
+        <v>0.9087</v>
       </c>
       <c r="G5" t="n">
         <v>5.768</v>
@@ -844,13 +844,13 @@
         <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9082</v>
+        <v>1.2549</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9585</v>
+        <v>1.1071</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0504</v>
+        <v>0.1478</v>
       </c>
       <c r="V5" t="n">
         <v>-1.267</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2628</v>
+        <v>1.0849</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7016</v>
+        <v>0.2759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5612</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.1543</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9698</v>
+        <v>0.7919</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6471</v>
+        <v>1.2214</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6772</v>
+        <v>-0.4295</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2403</v>
+        <v>0.9436</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0164</v>
+        <v>1.7445</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7761</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1.3798</v>
@@ -1078,13 +1078,13 @@
         <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2399</v>
+        <v>0.9433</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0166</v>
+        <v>0.7447</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2233</v>
+        <v>0.1985</v>
       </c>
       <c r="V8" t="n">
         <v>-2.8455</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0268</v>
+        <v>-0.002</v>
       </c>
       <c r="E9" t="n">
         <v>-0.5044999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4777</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4098</v>
@@ -1156,13 +1156,13 @@
         <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1667</v>
+        <v>-0.142</v>
       </c>
       <c r="T9" t="n">
         <v>0.0732</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2399</v>
+        <v>-0.2151</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1566</v>
+        <v>-0.0286</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0785</v>
+        <v>-0.3081</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.2795</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5121</v>
+        <v>0.8036</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4206</v>
+        <v>0.2781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9327</v>
+        <v>0.5256</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0876</v>
+        <v>1.2145</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.796</v>
+        <v>0.4644</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7085</v>
+        <v>0.7501</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5997</v>
+        <v>-0.4109</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3754</v>
+        <v>-0.1863</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2243</v>
+        <v>-0.2246</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R10" t="n">
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1035</v>
+        <v>0.1782</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8416</v>
+        <v>0.4932</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2618</v>
+        <v>-0.3151</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0508</v>
+        <v>-0.2608</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0753</v>
+        <v>-0.8403</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0245</v>
+        <v>0.5795</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3969</v>
+        <v>-0.3607</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8596</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2565</v>
+        <v>0.2084</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3415</v>
+        <v>-0.1177</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1392</v>
+        <v>-0.9353</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4808</v>
+        <v>0.8176</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9446</v>
+        <v>-0.243</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7204</v>
+        <v>0.3662</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2243</v>
+        <v>-0.6092</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2828</v>
+        <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.6783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>0.4661</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2029</v>
+        <v>0.2123</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0703</v>
+        <v>-0.3797</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0773</v>
+        <v>-2.6767</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007</v>
+        <v>2.297</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8036</v>
+        <v>-1.3969</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2781</v>
+        <v>0.8596</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5256</v>
+        <v>-2.2565</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2145</v>
+        <v>-2.3415</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4644</v>
+        <v>0.1392</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7501</v>
+        <v>-2.4808</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4109</v>
+        <v>0.9446</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1863</v>
+        <v>0.7204</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2246</v>
+        <v>0.2243</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8636</v>
+        <v>-0.0824</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.276</v>
+        <v>-0.152</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5876</v>
+        <v>0.0696</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4811</v>
+        <v>-0.6733</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9119</v>
+        <v>-1.2979</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4308</v>
+        <v>0.6246</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3607</v>
+        <v>0.5121</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.4206</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2084</v>
+        <v>0.9327</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1177</v>
+        <v>-0.0876</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9353</v>
+        <v>-0.796</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8176</v>
+        <v>0.7085</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.243</v>
+        <v>0.5997</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3662</v>
+        <v>0.3754</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6092</v>
+        <v>0.2243</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5419</v>
+        <v>0.5867</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6056</v>
+        <v>0.6222</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0636</v>
+        <v>-0.0355</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.945</v>
+        <v>-1.5889</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>-1.5889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.678</v>
+        <v>-3.0733</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6</v>
+        <v>-4.1192</v>
       </c>
       <c r="F14" t="n">
-        <v>0.922</v>
+        <v>1.0459</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6137</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6323</v>
+        <v>-0.0277</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.221</v>
+        <v>0.2598</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4114</v>
+        <v>-0.2875</v>
       </c>
       <c r="V14" t="n">
         <v>0.3011</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.9713</v>
+        <v>25.7971</v>
       </c>
       <c r="E15" t="n">
-        <v>9.766500000000006</v>
+        <v>10.5923</v>
       </c>
       <c r="F15" t="n">
-        <v>15.2047</v>
+        <v>15.2049</v>
       </c>
       <c r="G15" t="n">
         <v>10.7616</v>
@@ -1594,7 +1594,7 @@
         <v>10.4405</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3212999999999998</v>
+        <v>0.3212999999999995</v>
       </c>
       <c r="J15" t="n">
         <v>9.825800000000001</v>
@@ -1612,7 +1612,7 @@
         <v>1.098</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1620999999999999</v>
+        <v>-0.1621</v>
       </c>
       <c r="P15" t="n">
         <v>9.162800000000001</v>
@@ -1624,13 +1624,13 @@
         <v>21.9908</v>
       </c>
       <c r="S15" t="n">
-        <v>9.159299999999996</v>
+        <v>9.984800000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>8.593599999999999</v>
+        <v>9.419500000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5653999999999999</v>
+        <v>0.5655</v>
       </c>
       <c r="V15" t="n">
         <v>-4.1125</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0612</v>
+        <v>3.6906</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8855</v>
+        <v>3.9817</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8243</v>
+        <v>-0.2911</v>
       </c>
       <c r="G16" t="n">
         <v>0.8678</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0736</v>
+        <v>-0.4442</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1448</v>
+        <v>0.241</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2184</v>
+        <v>-0.6852</v>
       </c>
       <c r="V16" t="n">
         <v>2.5339</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2243</v>
+        <v>0.6409</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6131</v>
+        <v>-0.3247</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8374</v>
+        <v>0.9656</v>
       </c>
       <c r="G17" t="n">
         <v>0.2974</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2564</v>
+        <v>0.1603</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1471</v>
+        <v>0.1414</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1094</v>
+        <v>0.0188</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3296</v>
+        <v>-0.8157</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4174</v>
+        <v>-0.0593</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9122</v>
+        <v>-0.7564</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5628</v>
+        <v>-1.7664</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9665</v>
+        <v>-2.4077</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4037</v>
+        <v>0.6413</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.471</v>
+        <v>-1.2866</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5543</v>
+        <v>-1.4154</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0833</v>
+        <v>0.1288</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0919</v>
+        <v>-0.4798</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4122</v>
+        <v>-0.9923</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3204</v>
+        <v>0.5125</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R18" t="n">
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7826</v>
+        <v>-1.777</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0536</v>
+        <v>-0.2175</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8361</v>
+        <v>-1.5594</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.267</v>
+        <v>2.5444</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5444</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3417</v>
+        <v>-0.9639</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1555</v>
+        <v>-0.6097</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1862</v>
+        <v>-0.3541</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7664</v>
+        <v>-0.5628</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4077</v>
+        <v>-0.9665</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6413</v>
+        <v>0.4037</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2866</v>
+        <v>-0.471</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4154</v>
+        <v>-0.5543</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1288</v>
+        <v>0.0833</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4798</v>
+        <v>-0.0919</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9923</v>
+        <v>-0.4122</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5125</v>
+        <v>0.3204</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3029</v>
+        <v>-0.4169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3137</v>
+        <v>-0.1387</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.9892</v>
+        <v>-0.2781</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5444</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5444</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2561</v>
+        <v>-3.0361</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0402</v>
+        <v>-1.944</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2159</v>
+        <v>-1.0921</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2913</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5041</v>
+        <v>-0.2841</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2021</v>
+        <v>-0.106</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.302</v>
+        <v>-0.1782</v>
       </c>
       <c r="V20" t="n">
         <v>-0.0104</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.532</v>
+        <v>-3.3019</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5787</v>
+        <v>-1.0017</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9534</v>
+        <v>-2.3002</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7895</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4756</v>
+        <v>-1.2455</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8265</v>
+        <v>-0.2496</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6491</v>
+        <v>-0.9959</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0089</v>
+        <v>-3.8909</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.419</v>
+        <v>-2.6114</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5899</v>
+        <v>-1.2796</v>
       </c>
       <c r="G22" t="n">
         <v>1.5325</v>
@@ -2170,13 +2170,13 @@
         <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2765</v>
+        <v>-1.1586</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1991</v>
+        <v>0.0068</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4757</v>
+        <v>-1.1654</v>
       </c>
       <c r="V22" t="n">
         <v>1.5993</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8375</v>
+        <v>-6.6904</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.1165</v>
+        <v>-7.9242</v>
       </c>
       <c r="F23" t="n">
-        <v>1.279</v>
+        <v>1.2338</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6128</v>
@@ -2248,13 +2248,13 @@
         <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.921</v>
+        <v>-0.7739</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0935</v>
+        <v>0.0988</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8276</v>
+        <v>-0.8728</v>
       </c>
       <c r="V23" t="n">
         <v>0.6127</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.951</v>
+        <v>-8.680899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3731</v>
+        <v>-5.3346</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5779</v>
+        <v>-3.3462</v>
       </c>
       <c r="G24" t="n">
         <v>0.5633</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5663</v>
+        <v>-1.2962</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6199</v>
+        <v>-0.3416</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1862</v>
+        <v>-0.9546</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9005</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.9713</v>
+        <v>-23.0483</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.828</v>
+        <v>-15.8279</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.1434</v>
+        <v>-7.2203</v>
       </c>
       <c r="G25" t="n">
         <v>-10.7618</v>
@@ -2404,13 +2404,13 @@
         <v>12.828</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.159000000000001</v>
+        <v>-7.2361</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5655</v>
+        <v>-0.5654</v>
       </c>
       <c r="U25" t="n">
-        <v>-8.5937</v>
+        <v>-6.6708</v>
       </c>
       <c r="V25" t="n">
         <v>4.1124</v>
